--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:51</t>
+    <t xml:space="preserve">2026-09-24 01:41</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -845,19 +845,19 @@
         <v>25</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.1</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.12</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.26</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="16">
@@ -891,19 +891,19 @@
         <v>25</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>0.46</v>
+        <v>0.21</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>15</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.14</v>
+        <v>0.2</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
@@ -96,7 +96,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:41</t>
+    <t xml:space="preserve">2026-10-01 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mat_a_2023_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:12</t>
+    <t xml:space="preserve">2026-10-05 20:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
